--- a/bts-gpme/tp-1083/ressources/R02_Registre_evenements_SST_et_cotation.xlsx
+++ b/bts-gpme/tp-1083/ressources/R02_Registre_evenements_SST_et_cotation.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidents" sheetId="1" r:id="R2dbb4cf445bc4b12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grille_DUERP" sheetId="2" r:id="R18cb67ef642c4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incidents" sheetId="1" r:id="Reb2acf3e94ab4fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grille_DUERP" sheetId="2" r:id="R0b1738b0cbeb4f6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contrôle_données" sheetId="3" r:id="R3dc0c143f630465c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +18,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +46,14 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,6 +80,16 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F5F78"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -81,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -134,6 +151,28 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -889,9 +928,7 @@
       <x:c r="I18" s="16" t="str">
         <x:v>Arrêt d'urgence machine</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="str">
-        <x:v>Ligne potentiellement dupliquée dans le registre.</x:v>
-      </x:c>
+      <x:c r="J18" s="16" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="16" t="str">
@@ -931,7 +968,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13d50b1d3b0941a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03d4905a5261439a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1052,7 +1089,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>Score brut P×G</x:v>
+        <x:v>Criticité P×G</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
         <x:v>1 à 5</x:v>
@@ -1104,17 +1141,17 @@
       <x:c r="C14" s="16"/>
       <x:c r="D14" s="16"/>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="62" customHeight="1">
       <x:c r="A15" s="16" t="str">
         <x:v>Consigne</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
-        <x:v>Tenez compte des mesures existantes pour réévaluer le risque et proposer les actions complémentaires.</x:v>
+        <x:v>Tenez compte des mesures existantes pour réévaluer le risque et proposer les actions complémentaires. Une mesure existante n’est pas nécessairement efficace.</x:v>
       </x:c>
       <x:c r="C15" s="16"/>
       <x:c r="D15" s="16"/>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Règle de vigilance</x:v>
       </x:c>
@@ -1124,7 +1161,7 @@
       <x:c r="C16" s="24"/>
       <x:c r="D16" s="24"/>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="16" t="str">
         <x:v>Contrôle</x:v>
       </x:c>
@@ -1133,6 +1170,14 @@
       </x:c>
       <x:c r="C17" s="16"/>
       <x:c r="D17" s="16"/>
+    </x:row>
+    <x:row r="18" ht="62" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>Consigne</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="str">
+        <x:v>La gravité s’apprécie à partir du dommage potentiel plausible, et non seulement du dommage effectivement observé lors du dernier événement.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1140,4 +1185,159 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="28" t="str">
+        <x:v>TRACE DE CONTRÔLE — consignez les anomalies repérées avant tout calcul ; ne supprimez aucune donnée sans justification.</x:v>
+      </x:c>
+      <x:c r="B1" s="28"/>
+      <x:c r="C1" s="28"/>
+      <x:c r="D1" s="28"/>
+      <x:c r="E1" s="28"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="33" t="str">
+        <x:v>ID concerné</x:v>
+      </x:c>
+      <x:c r="B3" s="33" t="str">
+        <x:v>Anomalie constatée</x:v>
+      </x:c>
+      <x:c r="C3" s="33" t="str">
+        <x:v>Décision prise</x:v>
+      </x:c>
+      <x:c r="D3" s="33" t="str">
+        <x:v>Justification</x:v>
+      </x:c>
+      <x:c r="E3" s="33" t="str">
+        <x:v>Information à confirmer</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="38" customHeight="1">
+      <x:c r="A4" s="34" t="str"/>
+      <x:c r="B4" s="34" t="str"/>
+      <x:c r="C4" s="34" t="str"/>
+      <x:c r="D4" s="34" t="str"/>
+      <x:c r="E4" s="34" t="str"/>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
+      <x:c r="A5" s="34" t="str"/>
+      <x:c r="B5" s="34" t="str"/>
+      <x:c r="C5" s="34" t="str"/>
+      <x:c r="D5" s="34" t="str"/>
+      <x:c r="E5" s="34" t="str"/>
+    </x:row>
+    <x:row r="6" ht="38" customHeight="1">
+      <x:c r="A6" s="34" t="str"/>
+      <x:c r="B6" s="34" t="str"/>
+      <x:c r="C6" s="34" t="str"/>
+      <x:c r="D6" s="34" t="str"/>
+      <x:c r="E6" s="34" t="str"/>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" s="34" t="str"/>
+      <x:c r="B7" s="34" t="str"/>
+      <x:c r="C7" s="34" t="str"/>
+      <x:c r="D7" s="34" t="str"/>
+      <x:c r="E7" s="34" t="str"/>
+    </x:row>
+    <x:row r="8" ht="38" customHeight="1">
+      <x:c r="A8" s="34" t="str"/>
+      <x:c r="B8" s="34" t="str"/>
+      <x:c r="C8" s="34" t="str"/>
+      <x:c r="D8" s="34" t="str"/>
+      <x:c r="E8" s="34" t="str"/>
+    </x:row>
+    <x:row r="9" ht="38" customHeight="1">
+      <x:c r="A9" s="34" t="str"/>
+      <x:c r="B9" s="34" t="str"/>
+      <x:c r="C9" s="34" t="str"/>
+      <x:c r="D9" s="34" t="str"/>
+      <x:c r="E9" s="34" t="str"/>
+    </x:row>
+    <x:row r="10" ht="38" customHeight="1">
+      <x:c r="A10" s="34" t="str"/>
+      <x:c r="B10" s="34" t="str"/>
+      <x:c r="C10" s="34" t="str"/>
+      <x:c r="D10" s="34" t="str"/>
+      <x:c r="E10" s="34" t="str"/>
+    </x:row>
+    <x:row r="11" ht="38" customHeight="1">
+      <x:c r="A11" s="34" t="str"/>
+      <x:c r="B11" s="34" t="str"/>
+      <x:c r="C11" s="34" t="str"/>
+      <x:c r="D11" s="34" t="str"/>
+      <x:c r="E11" s="34" t="str"/>
+    </x:row>
+    <x:row r="12" ht="38" customHeight="1">
+      <x:c r="A12" s="34" t="str"/>
+      <x:c r="B12" s="34" t="str"/>
+      <x:c r="C12" s="34" t="str"/>
+      <x:c r="D12" s="34" t="str"/>
+      <x:c r="E12" s="34" t="str"/>
+    </x:row>
+    <x:row r="13" ht="38" customHeight="1">
+      <x:c r="A13" s="34" t="str"/>
+      <x:c r="B13" s="34" t="str"/>
+      <x:c r="C13" s="34" t="str"/>
+      <x:c r="D13" s="34" t="str"/>
+      <x:c r="E13" s="34" t="str"/>
+    </x:row>
+    <x:row r="14" ht="38" customHeight="1">
+      <x:c r="A14" s="34" t="str"/>
+      <x:c r="B14" s="34" t="str"/>
+      <x:c r="C14" s="34" t="str"/>
+      <x:c r="D14" s="34" t="str"/>
+      <x:c r="E14" s="34" t="str"/>
+    </x:row>
+    <x:row r="15" ht="38" customHeight="1">
+      <x:c r="A15" s="34" t="str"/>
+      <x:c r="B15" s="34" t="str"/>
+      <x:c r="C15" s="34" t="str"/>
+      <x:c r="D15" s="34" t="str"/>
+      <x:c r="E15" s="34" t="str"/>
+    </x:row>
+    <x:row r="16" ht="38" customHeight="1">
+      <x:c r="A16" s="34" t="str"/>
+      <x:c r="B16" s="34" t="str"/>
+      <x:c r="C16" s="34" t="str"/>
+      <x:c r="D16" s="34" t="str"/>
+      <x:c r="E16" s="34" t="str"/>
+    </x:row>
+    <x:row r="17" ht="38" customHeight="1">
+      <x:c r="A17" s="34" t="str"/>
+      <x:c r="B17" s="34" t="str"/>
+      <x:c r="C17" s="34" t="str"/>
+      <x:c r="D17" s="34" t="str"/>
+      <x:c r="E17" s="34" t="str"/>
+    </x:row>
+    <x:row r="18" ht="38" customHeight="1">
+      <x:c r="A18" s="34" t="str"/>
+      <x:c r="B18" s="34" t="str"/>
+      <x:c r="C18" s="34" t="str"/>
+      <x:c r="D18" s="34" t="str"/>
+      <x:c r="E18" s="34" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="C4:C18">
+      <x:formula1>"Conserver,Corriger,Écarter temporairement,À confirmer"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/bts-gpme/tp-1083/ressources/R02_Registre_evenements_SST_et_cotation.xlsx
+++ b/bts-gpme/tp-1083/ressources/R02_Registre_evenements_SST_et_cotation.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\COURS\_deploy\tp1083-sst-hotfix-20260923\bts-gpme\tp-1083\ressources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C0B319-7DCB-4A74-9699-570A85BE9767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="3480" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="3480" windowWidth="19420" windowHeight="10300"/>
   </bookViews>
   <sheets>
-    <sheet name="Incidents" sheetId="1" r:id="rId1"/>
-    <sheet name="Grille_DUERP" sheetId="2" r:id="rId2"/>
-    <sheet name="Contrôle_données" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Incidents" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Grille_DUERP" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Contrôle_données" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -114,12 +108,18 @@
     <t>Accident bénin</t>
   </si>
   <si>
+    <t>Douleur au dos signalée pendant une opération de réception.</t>
+  </si>
+  <si>
     <t>Hebdomadaire</t>
   </si>
   <si>
     <t>Diable disponible</t>
   </si>
   <si>
+    <t>Circonstances non détaillées dans le registre ; informations à compléter.</t>
+  </si>
+  <si>
     <t>INC-04</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t>Occasionnelle</t>
   </si>
   <si>
-    <t>Tamcs d'entrée</t>
+    <t>Tapis d'entrée</t>
   </si>
   <si>
     <t>Aucun panneau temporaire disponible.</t>
@@ -451,39 +451,40 @@
   </si>
   <si>
     <t>Information à confirmer / vérification à mener</t>
-  </si>
-  <si>
-    <t>Douleur au dos signalée pendant une opération de réception.</t>
-  </si>
-  <si>
-    <t>Circonstances non détaillées dans le registre ; informations à compléter.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF6A4A00"/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF173F45"/>
       <sz val="11"/>
-      <color rgb="FF6A4A00"/>
       <name val="Carlito"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FF173F45"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -493,8 +494,8 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF7F6000"/>
       <sz val="11"/>
-      <color rgb="FF7F6000"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -543,38 +544,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -594,18 +592,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="IncidentsTable" displayName="IncidentsTable" ref="A3:J19" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="IncidentsTable" displayName="IncidentsTable" ref="A3:J19" totalsRowShown="1" headerRowCount="0">
+  <autoFilter>
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+  </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Unité de travail"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Poste / activité"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nature de l'événement"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Description synthétique"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Arrêt (jours)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Fréquence d'exposition"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Mesures existantes"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Signalement / observation"/>
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="Unité de travail"/>
+    <tableColumn id="4" name="Poste / activité"/>
+    <tableColumn id="5" name="Nature de l'événement"/>
+    <tableColumn id="6" name="Description synthétique"/>
+    <tableColumn id="7" name="Arrêt (jours)"/>
+    <tableColumn id="8" name="Fréquence d'exposition"/>
+    <tableColumn id="9" name="Mesures existantes"/>
+    <tableColumn id="10" name="Signalement / observation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -805,9 +815,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.7265625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -821,558 +831,558 @@
     <col min="10" max="10" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="21.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="3" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>46041</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="4">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>46056</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="4">
         <v>0</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>46079</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="F6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="I6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="3">
+      <c r="J6" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="5">
         <v>46099</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="2">
+      <c r="E7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="I7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3">
+      <c r="J7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="5">
         <v>46119</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="F8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="H8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="3">
+      <c r="J8" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="5">
         <v>46141</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="C9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46154</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46170</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="5">
+        <v>46189</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="5">
+        <v>46203</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46212</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46227</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46259</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" ht="29" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46276</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="D19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="4">
+        <v>2</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="3">
-        <v>46154</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46170</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46189</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="3">
-        <v>46203</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="3">
-        <v>46212</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="3">
-        <v>46227</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" s="3">
-        <v>46259</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="3">
-        <v>46268</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="3">
-        <v>46268</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" s="3">
-        <v>46276</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="2">
-        <v>2</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>99</v>
+      <c r="I19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1387,9 +1397,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.7265625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1397,204 +1407,204 @@
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="1" ht="21.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" ht="29" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+      <c r="C3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+      <c r="C4" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+      <c r="C5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" ht="29" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+      <c r="C6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+      <c r="C7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D8" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="1" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" ht="29" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" ht="43.5" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" ht="41.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B16" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" ht="41.4" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1606,9 +1616,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="8.7265625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
@@ -1616,150 +1626,153 @@
     <col min="5" max="5" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-    </row>
-    <row r="12" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18" spans="1:5" ht="25.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D3" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+    </row>
+    <row r="6" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+    </row>
+    <row r="7" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+    </row>
+    <row r="8" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" ht="25.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="C4:C18" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="C10:C18">
+      <formula1>"Conserver,Corriger,Écarter temporairement,À confirmer"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="C4:C18">
       <formula1>"Conserver,Corriger,Écarter temporairement,À confirmer"</formula1>
     </dataValidation>
   </dataValidations>
